--- a/SEO_IMPLEMENTATION_REPORT.xlsx
+++ b/SEO_IMPLEMENTATION_REPORT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NASEER KHAN\myproject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D4BE0-E0AE-496B-B096-7E072FAB5F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4860991D-3FBA-44C1-977F-A9F80B7C6F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5160" yWindow="2580" windowWidth="11550" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -766,7 +766,7 @@
     <t>Resolved - not an issue</t>
   </si>
   <si>
-    <t>All 12 trigger predicates are custom-event equality checks (_eq {{event}}, ...). No gtm.formSubmit, gtm.linkClick or gtm.historyChange trigger fires any tag.</t>
+    <t>Confirmed by parsing the live container: all 12 triggers are custom-event equality checks. No gtm.formSubmit / gtm.linkClick / gtm.historyChange trigger is bound to any tag. Built-in listeners push to dataLayer but nothing consumes them.</t>
   </si>
   <si>
     <t>None. The built-in listeners push to dataLayer but no tag consumes them.</t>
@@ -781,7 +781,7 @@
     <t>P1 - Blocking</t>
   </si>
   <si>
-    <t>Tag 25 and tag 48 are both GA4 Event tags with eventName generate_lead, both sending to G-N2VGBEBELF, both firing on the same generate_lead trigger.</t>
+    <t>Tag ID 25 (7 params incl page_path/page_title/form_name) and tag ID 48 (4 params: lead_type, service_name, currency, value) both fire GA4 generate_lead to G-N2VGBEBELF on the same custom-event trigger. KEEP 25, PAUSE 48.</t>
   </si>
   <si>
     <t>Every lead is recorded TWICE in GA4. Conversion counts and rates in GA4 are inflated by 100 percent.</t>
@@ -796,7 +796,7 @@
     <t>Correct</t>
   </si>
   <si>
-    <t>Exactly one __awct tag (id 49), conversion ID 18246691744, label J2SlCMja0M0cEKDX2fxD, firing on generate_lead only.</t>
+    <t>Exactly one __awct tag (ID 49), conversion ID 18246691744, label J2SlCMja0M0cEKDX2fxD, firing on generate_lead only. Verify in the Ads account that no GA4-IMPORTED conversion action also counts leads alongside this tag.</t>
   </si>
   <si>
     <t>Google Ads conversions are NOT duplicated.</t>
@@ -2105,7 +2105,7 @@
     <col min="3" max="3" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3651,7 +3651,7 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>178</v>
       </c>
@@ -4291,7 +4291,7 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>232</v>
       </c>
@@ -6026,7 +6026,7 @@
     <col min="5" max="5" width="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>495</v>
       </c>
